--- a/branches/master/observations-summary.xlsx
+++ b/branches/master/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="312">
   <si>
     <t>Profile</t>
   </si>
@@ -200,6 +200,18 @@
     <t>null#251852001, null#9103-3, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-bilanz-einfuhr-kalorien-24h</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Kalorien 24h</t>
+  </si>
+  <si>
+    <t>null#787787004, null#9057-1, null#null</t>
+  </si>
+  <si>
+    <t>Periodĵ</t>
+  </si>
+  <si>
     <t>mii-pr-icu-bilanz-einfuhr-muttermilch</t>
   </si>
   <si>
@@ -266,24 +278,6 @@
     <t>null#444479000, null#null, null#null</t>
   </si>
   <si>
-    <t>mii-pr-icu-ect-blutfluss-extrakorporaler-gasaustausch</t>
-  </si>
-  <si>
-    <t>MII PR ICU Blutfluss Extrakorporaler Gasaustausch</t>
-  </si>
-  <si>
-    <t>null#251288004, null#null, null#null</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-ect-blutflussindex-extrakorporaler-gasaustausch</t>
-  </si>
-  <si>
-    <t>MII PR ICU Blutflussindex Extrakorporaler Gasaustausch</t>
-  </si>
-  <si>
-    <t>null#251289007, null#null, null#null</t>
-  </si>
-  <si>
     <t>mii-pr-icu-ect-dauer-extrakorporaler-gasaustausch</t>
   </si>
   <si>
@@ -320,15 +314,6 @@
     <t>null#401000124105, null#null, null#null</t>
   </si>
   <si>
-    <t>mii-pr-icu-ect-ionisiertes-kalzium-nierenersatzverfahren</t>
-  </si>
-  <si>
-    <t>MII PR ICU Ionisiertes Kalzium Nierenersatzverfahren</t>
-  </si>
-  <si>
-    <t>null#null, null#83064-6, null#null</t>
-  </si>
-  <si>
     <t>mii-pr-icu-ect-substituatfluss</t>
   </si>
   <si>
@@ -777,6 +762,15 @@
   </si>
   <si>
     <t>null#250819002, null#76334-2, null#16929632</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-vent-einstellung-inspirationsdruck</t>
+  </si>
+  <si>
+    <t>MII PR ICU Einstellung Inspirationsdruck</t>
+  </si>
+  <si>
+    <t>null#76003-3, null#151972</t>
   </si>
   <si>
     <t>mii-pr-icu-vent-endexpiratorischer-kohlendioxidpartialdruck</t>
@@ -1087,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1670,7 +1664,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -1687,10 +1681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -1699,7 +1693,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>16</v>
@@ -1722,10 +1716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1734,7 +1728,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>16</v>
@@ -1757,10 +1751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1769,7 +1763,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>16</v>
@@ -1792,10 +1786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1804,7 +1798,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>16</v>
@@ -1827,13 +1821,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
@@ -1868,13 +1862,13 @@
         <v>82</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>16</v>
@@ -1897,19 +1891,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>16</v>
@@ -1932,19 +1926,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>16</v>
@@ -1967,19 +1961,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>16</v>
@@ -2002,19 +1996,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>16</v>
@@ -2037,19 +2031,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>16</v>
@@ -2072,19 +2066,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>16</v>
@@ -2107,19 +2101,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>16</v>
@@ -2142,19 +2136,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>16</v>
@@ -2177,31 +2171,31 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>14</v>
@@ -2212,25 +2206,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -2247,31 +2241,31 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="F34" t="s" s="2">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>14</v>
@@ -2285,7 +2279,7 @@
         <v>14</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>14</v>
@@ -2294,7 +2288,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>
@@ -2317,25 +2311,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -2352,25 +2346,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -2387,28 +2381,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>19</v>
@@ -2422,28 +2416,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="D39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H39" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>19</v>
@@ -2457,28 +2451,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>19</v>
@@ -2492,34 +2486,34 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>14</v>
@@ -2527,19 +2521,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>16</v>
@@ -2562,34 +2556,34 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>14</v>
@@ -2597,19 +2591,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>16</v>
@@ -2618,7 +2612,7 @@
         <v>17</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
@@ -2632,28 +2626,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="B45" t="s" s="2">
-        <v>148</v>
-      </c>
       <c r="C45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
@@ -2667,28 +2661,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>19</v>
@@ -2705,7 +2699,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>14</v>
@@ -2723,7 +2717,7 @@
         <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>19</v>
@@ -2740,7 +2734,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2758,7 +2752,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -2772,28 +2766,28 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="C49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F49" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
@@ -2807,28 +2801,28 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>19</v>
@@ -2842,64 +2836,64 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="F51" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H52" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="D52" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="I52" t="s" s="2">
         <v>19</v>
       </c>
@@ -2907,7 +2901,7 @@
         <v>14</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>14</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53">
@@ -2915,7 +2909,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>14</v>
@@ -2933,7 +2927,7 @@
         <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -2942,33 +2936,33 @@
         <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>19</v>
@@ -2977,7 +2971,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>162</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -2985,7 +2979,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -3003,7 +2997,7 @@
         <v>14</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -3012,33 +3006,33 @@
         <v>14</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>163</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>19</v>
@@ -3055,7 +3049,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>14</v>
@@ -3073,7 +3067,7 @@
         <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -3090,7 +3084,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -3108,7 +3102,7 @@
         <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -3125,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -3143,7 +3137,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -3160,7 +3154,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>14</v>
@@ -3178,7 +3172,7 @@
         <v>14</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -3195,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>14</v>
@@ -3213,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
@@ -3230,7 +3224,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -3248,7 +3242,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>19</v>
@@ -3262,28 +3256,28 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="B63" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="C63" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F63" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>19</v>
@@ -3297,28 +3291,28 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>19</v>
@@ -3332,19 +3326,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>16</v>
@@ -3353,7 +3347,7 @@
         <v>17</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
@@ -3367,13 +3361,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
@@ -3382,13 +3376,13 @@
         <v>174</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>175</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>19</v>
@@ -3402,28 +3396,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>19</v>
@@ -3440,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>14</v>
@@ -3449,7 +3443,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>14</v>
@@ -3458,7 +3452,7 @@
         <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>19</v>
@@ -3475,17 +3469,17 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="C69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
       </c>
@@ -3493,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>19</v>
@@ -3510,7 +3504,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>14</v>
@@ -3519,7 +3513,7 @@
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>14</v>
@@ -3528,7 +3522,7 @@
         <v>14</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>19</v>
@@ -3545,7 +3539,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>14</v>
@@ -3554,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>14</v>
@@ -3563,7 +3557,7 @@
         <v>14</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>19</v>
@@ -3577,28 +3571,28 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>19</v>
@@ -3612,28 +3606,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
@@ -3647,28 +3641,28 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C74" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H74" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="D74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="F74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>19</v>
@@ -3682,31 +3676,31 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>14</v>
@@ -3717,28 +3711,28 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G76" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="C76" t="s" s="2">
+      <c r="H76" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="D76" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E76" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="F76" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>19</v>
@@ -3752,31 +3746,31 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>14</v>
@@ -3787,28 +3781,28 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>19</v>
@@ -3822,28 +3816,28 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>19</v>
@@ -3857,34 +3851,34 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>14</v>
@@ -3892,28 +3886,28 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>19</v>
@@ -3927,34 +3921,34 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B82" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C82" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="C82" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="D82" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>215</v>
+        <v>14</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>14</v>
@@ -3962,22 +3956,22 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>17</v>
@@ -3997,22 +3991,22 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>17</v>
@@ -4032,19 +4026,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>16</v>
@@ -4067,22 +4061,22 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>17</v>
@@ -4102,22 +4096,22 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B87" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="F87" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="D87" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E87" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>17</v>
@@ -4137,22 +4131,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>17</v>
@@ -4172,22 +4166,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>17</v>
@@ -4207,22 +4201,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>17</v>
@@ -4242,22 +4236,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>17</v>
@@ -4277,22 +4271,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>17</v>
@@ -4312,22 +4306,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>17</v>
@@ -4347,19 +4341,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>16</v>
@@ -4382,22 +4376,22 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>17</v>
@@ -4417,22 +4411,22 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>17</v>
@@ -4452,22 +4446,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>17</v>
@@ -4487,22 +4481,22 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>17</v>
@@ -4522,22 +4516,22 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>17</v>
@@ -4557,22 +4551,22 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>17</v>
@@ -4592,22 +4586,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>17</v>
@@ -4627,22 +4621,22 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>17</v>
@@ -4662,19 +4656,19 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>16</v>
@@ -4697,19 +4691,19 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>14</v>
+        <v>213</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>16</v>
@@ -4732,19 +4726,19 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>16</v>
@@ -4767,19 +4761,19 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>16</v>
@@ -4802,22 +4796,22 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>17</v>
@@ -4837,22 +4831,22 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>17</v>
@@ -4872,22 +4866,22 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>17</v>
@@ -4907,22 +4901,22 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>17</v>
@@ -4942,22 +4936,22 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>17</v>
@@ -4977,22 +4971,22 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F112" t="s" s="2">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>17</v>
@@ -5007,41 +5001,6 @@
         <v>14</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="D113" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E113" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="F113" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K113" t="s" s="2">
         <v>14</v>
       </c>
     </row>
